--- a/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_4.xlsx
+++ b/amostras/amostras_xlsx/Pesquisa_Eleitoral_Amostra_4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D7F89C1-808B-CB47-9185-4B1BC5CADB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54B82199-B3FC-1043-B334-EC5DA49693C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="36">
   <si>
     <t>Faixa de renda familiar</t>
   </si>
@@ -1439,29 +1439,6 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A72" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s">
-        <v>20</v>
-      </c>
-      <c r="C72" t="s">
-        <v>20</v>
-      </c>
-      <c r="D72" t="s">
-        <v>18</v>
-      </c>
-      <c r="E72" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G72" t="s">
-        <v>29</v>
-      </c>
-    </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>5</v>
